--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.92650789498182</v>
+        <v>7.300557532934547</v>
       </c>
       <c r="D2" t="n">
-        <v>44.18142699274792</v>
+        <v>7.179481886321536</v>
       </c>
       <c r="E2" t="n">
-        <v>9.79917645449877</v>
+        <v>1.59236617385605</v>
       </c>
       <c r="F2" t="n">
-        <v>10.44295099660666</v>
+        <v>1.696979536948583</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.52486080397937</v>
+        <v>10.48528988064665</v>
       </c>
       <c r="D3" t="n">
-        <v>65.06732898596124</v>
+        <v>10.5734409602187</v>
       </c>
       <c r="E3" t="n">
-        <v>9.79917645449877</v>
+        <v>1.59236617385605</v>
       </c>
       <c r="F3" t="n">
-        <v>10.44295099660666</v>
+        <v>1.696979536948583</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
